--- a/inst/schema/Draft_ExperimentHub_Manifest.xlsx
+++ b/inst/schema/Draft_ExperimentHub_Manifest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\priscilla.glenn\Documents\SbCompendium\inst\schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD249B0F-F076-410A-82F7-7C099E126130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447F79BB-5C1E-43D2-9BE9-6FA4BF601B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9213,10 +9213,12 @@
   <dimension ref="A1:N913"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="3" width="18" customWidth="1"/>
+    <col min="1" max="1" width="58.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="14" width="18" customWidth="1"/>
+    <col min="5" max="5" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="14" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
@@ -46268,9 +46270,10 @@
   <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="6" width="18" customWidth="1"/>
+    <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="131.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="42" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
@@ -46733,7 +46736,8 @@
   <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="18" customWidth="1"/>
+    <col min="1" max="1" width="15.9140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="90.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1">
